--- a/reports/pdf_rolling5_20260810.xlsx
+++ b/reports/pdf_rolling5_20260810.xlsx
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1214576000</v>
+        <v>453200000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.76%→0.99%</t>
+          <t>1.03%→1.14%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>53→75</t>
+          <t>211→233</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -922,23 +922,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>453200000</v>
+        <v>1214576000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.14%</t>
+          <t>0.76%→0.99%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>211→233</t>
+          <t>53→75</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2030,23 +2030,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>33630000</v>
+        <v>40527000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.80%</t>
+          <t>0.94%→1.09%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>306→321</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -2074,23 +2074,23 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>40527000</v>
+        <v>33630000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.09%</t>
+          <t>2.68%→2.80%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>306→321</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -2206,23 +2206,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>42864000</v>
+        <v>53990400</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.84%</t>
+          <t>2.67%→2.87%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2294,23 +2294,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>53990400</v>
+        <v>42864000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.87%</t>
+          <t>2.68%→2.84%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G54" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260810.xlsx
+++ b/reports/pdf_rolling5_20260810.xlsx
@@ -2030,23 +2030,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>40527000</v>
+        <v>33630000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.09%</t>
+          <t>2.68%→2.80%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>89→104</t>
+          <t>306→321</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -2074,23 +2074,23 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>33630000</v>
+        <v>40527000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.80%</t>
+          <t>0.94%→1.09%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>306→321</t>
+          <t>89→104</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -2162,23 +2162,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>26037600</v>
+        <v>42864000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.90%→1.00%</t>
+          <t>2.68%→2.84%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2206,23 +2206,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>53990400</v>
+        <v>40264800</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.87%</t>
+          <t>2.33%→2.48%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>89→95</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2250,23 +2250,23 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>40264800</v>
+        <v>26037600</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>2.33%→2.48%</t>
+          <t>0.90%→1.00%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>89→95</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -2294,23 +2294,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>42864000</v>
+        <v>53990400</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.84%</t>
+          <t>2.67%→2.87%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G54" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260810.xlsx
+++ b/reports/pdf_rolling5_20260810.xlsx
@@ -2162,23 +2162,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>42864000</v>
+        <v>53990400</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.84%</t>
+          <t>2.67%→2.87%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>76→82</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2294,23 +2294,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>53990400</v>
+        <v>42864000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.87%</t>
+          <t>2.68%→2.84%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>76→82</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G54" s="17" t="n"/>
